--- a/data/trans_dic/IP04D$notiene-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,65</t>
+          <t>2,53; 8,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 18,66</t>
+          <t>9,32; 18,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 26,03</t>
+          <t>11,21; 27,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,87</t>
+          <t>2,02; 8,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,01; 21,15</t>
+          <t>9,73; 20,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 13,68</t>
+          <t>3,49; 13,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,21</t>
+          <t>2,86; 7,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 17,88</t>
+          <t>11,01; 17,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,25; 18,55</t>
+          <t>8,23; 18,26</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,73</t>
+          <t>1,71; 5,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 15,92</t>
+          <t>8,51; 15,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 20,42</t>
+          <t>9,79; 20,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,48</t>
+          <t>1,99; 6,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 18,42</t>
+          <t>11,37; 18,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 15,95</t>
+          <t>7,43; 15,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 5,23</t>
+          <t>2,29; 5,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,8; 15,82</t>
+          <t>10,86; 15,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 16,77</t>
+          <t>9,86; 16,5</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,55</t>
+          <t>1,34; 6,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 18,14</t>
+          <t>9,99; 17,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 15,7</t>
+          <t>7,38; 15,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 8,8</t>
+          <t>2,53; 8,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,64; 22,03</t>
+          <t>12,96; 22,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,36; 25,2</t>
+          <t>12,99; 24,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,38</t>
+          <t>2,43; 6,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 18,4</t>
+          <t>12,3; 18,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 18,85</t>
+          <t>11,7; 19,31</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 8,94</t>
+          <t>2,76; 8,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 19,17</t>
+          <t>10,1; 19,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 20,49</t>
+          <t>9,11; 20,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,62</t>
+          <t>1,63; 6,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 19,22</t>
+          <t>9,71; 18,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 19,78</t>
+          <t>9,61; 19,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 6,5</t>
+          <t>2,75; 6,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,0; 17,68</t>
+          <t>11,5; 18,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,26</t>
+          <t>10,49; 18,42</t>
         </is>
       </c>
     </row>
@@ -1120,42 +1123,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,27</t>
+          <t>11,16; 15,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,82; 16,72</t>
+          <t>10,97; 16,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,5</t>
+          <t>2,97; 5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,81; 17,53</t>
+          <t>12,95; 17,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,98</t>
+          <t>11,33; 17,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,0</t>
+          <t>3,28; 5,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,53; 15,66</t>
+          <t>12,66; 15,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,04</t>
+          <t>11,79; 16,12</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6871</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18263</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10154</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6676</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>18012</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4645</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13547</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>36276</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>14799</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3648; 12167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12266; 24833</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6450; 16000</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2941; 12031</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12084; 25183</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2146; 8507</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8289; 20552</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>28154; 45310</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9788; 21716</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22779</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9670</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>37307</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>20270</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17722</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>61341</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>43049</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4040; 13353</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17748; 32218</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15589; 32072</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5336; 16191</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>29118; 46579</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>13519; 28746</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11553; 25573</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>50460; 73543</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>33652; 56273</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4938</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25190</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18631</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7856</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>31576</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38637</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12794</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>56766</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>57268</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2096; 9881</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18719; 33351</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12838; 26331</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4017; 13436</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24153; 41239</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>27485; 51359</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7638; 19795</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>45995; 68827</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>45083; 74410</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>9062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24498</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>38129</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24368</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>42003</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15397</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>48866</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>80132</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4723; 14691</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17435; 32889</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25012; 57545</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2932; 11229</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>16828; 32881</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>29350; 60776</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9673; 22203</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>39801; 62536</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>60855; 106809</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>28922</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>91985</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89694</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>105554</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>59459</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>203248</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>195248</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>21329; 39146</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>78140; 107958</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>72945; 110824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22306; 41019</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>95798; 131128</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>86163; 130400</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>47894; 74764</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>182313; 228599</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>168093; 229820</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$notiene-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,42</t>
+          <t>2,46; 8,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 18,86</t>
+          <t>9,98; 19,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 27,82</t>
+          <t>10,99; 27,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,28</t>
+          <t>1,96; 8,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 20,28</t>
+          <t>9,83; 19,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 13,85</t>
+          <t>3,84; 14,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 7,09</t>
+          <t>2,94; 7,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 17,71</t>
+          <t>11,07; 18,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,23; 18,26</t>
+          <t>7,99; 17,78</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,65</t>
+          <t>1,89; 5,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,46</t>
+          <t>8,46; 15,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 20,13</t>
+          <t>9,79; 20,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,03</t>
+          <t>1,96; 5,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,37; 18,19</t>
+          <t>11,23; 18,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 15,81</t>
+          <t>7,71; 15,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,07</t>
+          <t>2,38; 5,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 15,83</t>
+          <t>10,65; 15,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,86; 16,5</t>
+          <t>9,54; 16,31</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,32</t>
+          <t>1,34; 6,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,99; 17,79</t>
+          <t>9,75; 18,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 15,14</t>
+          <t>7,3; 15,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,47</t>
+          <t>2,57; 8,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,96; 22,13</t>
+          <t>12,84; 22,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 24,28</t>
+          <t>13,59; 25,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,29</t>
+          <t>2,51; 6,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 18,41</t>
+          <t>12,22; 18,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,7; 19,31</t>
+          <t>11,58; 19,11</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,57</t>
+          <t>3,1; 8,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 19,05</t>
+          <t>10,09; 18,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 20,97</t>
+          <t>8,94; 20,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,24</t>
+          <t>1,7; 6,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 18,97</t>
+          <t>10,03; 19,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 19,9</t>
+          <t>9,71; 19,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,32</t>
+          <t>2,89; 6,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 18,07</t>
+          <t>11,2; 17,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 18,42</t>
+          <t>10,42; 18,35</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,53</t>
+          <t>2,93; 5,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,42</t>
+          <t>11,36; 15,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,66</t>
+          <t>10,8; 16,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,45</t>
+          <t>2,95; 5,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,72</t>
+          <t>12,99; 17,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,15</t>
+          <t>11,3; 16,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,12</t>
+          <t>3,22; 4,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 15,87</t>
+          <t>12,6; 15,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,79; 16,12</t>
+          <t>11,83; 16,04</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3648; 12167</t>
+          <t>3560; 11923</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12266; 24833</t>
+          <t>13137; 25087</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6450; 16000</t>
+          <t>6318; 15647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2941; 12031</t>
+          <t>2851; 12777</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12084; 25183</t>
+          <t>12201; 24623</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2146; 8507</t>
+          <t>2361; 8867</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8289; 20552</t>
+          <t>8533; 21198</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28154; 45310</t>
+          <t>28322; 46439</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9788; 21716</t>
+          <t>9502; 21153</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4040; 13353</t>
+          <t>4470; 13696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17748; 32218</t>
+          <t>17628; 32254</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15589; 32072</t>
+          <t>15589; 33054</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5336; 16191</t>
+          <t>5261; 16076</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29118; 46579</t>
+          <t>28752; 47379</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13519; 28746</t>
+          <t>14017; 28548</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11553; 25573</t>
+          <t>11987; 26334</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>50460; 73543</t>
+          <t>49469; 73070</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33652; 56273</t>
+          <t>32557; 55625</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2096; 9881</t>
+          <t>2098; 9561</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18719; 33351</t>
+          <t>18272; 34142</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12838; 26331</t>
+          <t>12695; 26912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4017; 13436</t>
+          <t>4071; 14251</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24153; 41239</t>
+          <t>23937; 41126</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27485; 51359</t>
+          <t>28758; 54100</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7638; 19795</t>
+          <t>7899; 20838</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45995; 68827</t>
+          <t>45670; 69467</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>45083; 74410</t>
+          <t>44651; 73663</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4723; 14691</t>
+          <t>5303; 14754</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17435; 32889</t>
+          <t>17418; 32638</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25012; 57545</t>
+          <t>24532; 55813</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2932; 11229</t>
+          <t>3060; 11914</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16828; 32881</t>
+          <t>17388; 33204</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29350; 60776</t>
+          <t>29661; 60473</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9673; 22203</t>
+          <t>10165; 23633</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>39801; 62536</t>
+          <t>38744; 60279</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60855; 106809</t>
+          <t>60408; 106410</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21329; 39146</t>
+          <t>20748; 37967</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78140; 107958</t>
+          <t>79563; 105936</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72945; 110824</t>
+          <t>71831; 111837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22306; 41019</t>
+          <t>22184; 42082</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95798; 131128</t>
+          <t>96101; 128502</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86163; 130400</t>
+          <t>85913; 128326</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47894; 74764</t>
+          <t>47059; 72732</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>182313; 228599</t>
+          <t>181435; 227202</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>168093; 229820</t>
+          <t>168616; 228630</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$notiene-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,76%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13,87%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,25</t>
+          <t>2,05; 8,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 19,06</t>
+          <t>10,01; 21,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,99; 27,21</t>
+          <t>4,16; 15,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,79</t>
+          <t>2,51; 8,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 19,83</t>
+          <t>9,45; 18,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,84; 14,43</t>
+          <t>10,94; 27,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,31</t>
+          <t>2,79; 7,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,07; 18,15</t>
+          <t>10,99; 17,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 17,78</t>
+          <t>9,14; 20,13</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,8</t>
+          <t>2,05; 6,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 15,47</t>
+          <t>11,35; 18,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 20,75</t>
+          <t>7,11; 15,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,99</t>
+          <t>1,7; 5,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,23; 18,5</t>
+          <t>8,48; 15,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 15,7</t>
+          <t>8,48; 17,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,22</t>
+          <t>2,39; 5,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,65; 15,73</t>
+          <t>10,8; 15,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 16,31</t>
+          <t>9,08; 15,25</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>13,44%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>16,94%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,12</t>
+          <t>2,42; 8,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 18,22</t>
+          <t>12,64; 22,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,3; 15,48</t>
+          <t>12,43; 22,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,99</t>
+          <t>1,39; 6,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,84; 22,06</t>
+          <t>9,83; 18,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,59; 25,57</t>
+          <t>7,51; 15,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,62</t>
+          <t>2,4; 6,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,22; 18,58</t>
+          <t>12,41; 18,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,58; 19,11</t>
+          <t>10,74; 17,07</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,19%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 8,61</t>
+          <t>1,81; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 18,91</t>
+          <t>9,89; 19,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 20,34</t>
+          <t>8,3; 15,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,62</t>
+          <t>2,8; 8,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 19,15</t>
+          <t>10,38; 19,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 19,8</t>
+          <t>8,14; 15,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,73</t>
+          <t>2,93; 6,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,2; 17,42</t>
+          <t>11,0; 17,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 18,35</t>
+          <t>9,24; 14,18</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,36</t>
+          <t>2,96; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,13</t>
+          <t>12,81; 17,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,81</t>
+          <t>10,48; 15,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,59</t>
+          <t>3,01; 5,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,99; 17,36</t>
+          <t>11,14; 15,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,3; 16,88</t>
+          <t>10,2; 14,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,98</t>
+          <t>3,28; 5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,78</t>
+          <t>12,53; 15,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,04</t>
+          <t>10,79; 14,0</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6676</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18012</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>6871</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>18263</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10154</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6676</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>18012</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14051</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3560; 11923</t>
+          <t>2975; 12895</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13137; 25087</t>
+          <t>12431; 26261</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6318; 15647</t>
+          <t>2103; 7935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2851; 12777</t>
+          <t>3620; 12498</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12201; 24623</t>
+          <t>12446; 24565</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2361; 8867</t>
+          <t>5698; 14192</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8533; 21198</t>
+          <t>8088; 20890</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28322; 46439</t>
+          <t>28109; 45731</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9502; 21153</t>
+          <t>9385; 20659</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9670</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37307</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16647</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8051</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>24034</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22779</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9670</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37307</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20270</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43049</t>
+          <t>35233</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4470; 13696</t>
+          <t>5505; 17396</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17628; 32254</t>
+          <t>29057; 47179</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15589; 33054</t>
+          <t>11157; 23652</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5261; 16076</t>
+          <t>4010; 13533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28752; 47379</t>
+          <t>17671; 33177</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14017; 28548</t>
+          <t>12340; 25261</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11987; 26334</t>
+          <t>12051; 26370</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>49469; 73070</t>
+          <t>50166; 73482</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32557; 55625</t>
+          <t>27446; 46118</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>7856</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31576</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32801</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>4938</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>25190</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18631</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7856</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>31576</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57268</t>
+          <t>51620</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2098; 9561</t>
+          <t>3835; 13952</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18272; 34142</t>
+          <t>23557; 41067</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12695; 26912</t>
+          <t>24753; 44745</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4071; 14251</t>
+          <t>2168; 10228</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23937; 41126</t>
+          <t>18417; 34010</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28758; 54100</t>
+          <t>13179; 27217</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7899; 20838</t>
+          <t>7569; 20074</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45670; 69467</t>
+          <t>46378; 68775</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44651; 73663</t>
+          <t>40248; 63977</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>41</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6335</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24368</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33729</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>9062</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>24498</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38129</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24368</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>29608</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>80132</t>
+          <t>63336</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5303; 14754</t>
+          <t>3262; 11920</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17418; 32638</t>
+          <t>17143; 33318</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24532; 55813</t>
+          <t>24280; 45703</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3060; 11914</t>
+          <t>4791; 15317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17388; 33204</t>
+          <t>17921; 33091</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29661; 60473</t>
+          <t>20802; 38967</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10165; 23633</t>
+          <t>10303; 22822</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38744; 60279</t>
+          <t>38078; 61185</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60408; 106410</t>
+          <t>50662; 77732</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>87640</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>28922</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>91985</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89694</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>111264</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>164240</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20748; 37967</t>
+          <t>22281; 41389</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79563; 105936</t>
+          <t>94773; 129732</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71831; 111837</t>
+          <t>73275; 105461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22184; 42082</t>
+          <t>21305; 39198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96101; 128502</t>
+          <t>78028; 106883</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85913; 128326</t>
+          <t>64089; 90782</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47059; 72732</t>
+          <t>47920; 73045</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>181435; 227202</t>
+          <t>180428; 225587</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>168616; 228630</t>
+          <t>143231; 185929</t>
         </is>
       </c>
     </row>
